--- a/source/Dongwon/data(사전조사)/동원제품시장조사.xlsx
+++ b/source/Dongwon/data(사전조사)/동원제품시장조사.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\Dongwon\data(사전조사)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75C04F7-7C3A-43EE-9163-5B27F6EF1083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4781C57-C736-402F-977F-74ABF95127CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28860" yWindow="90" windowWidth="26955" windowHeight="13530" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29190" yWindow="240" windowWidth="26955" windowHeight="13530" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="제품별뉴스" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="245">
   <si>
     <t>product_name</t>
   </si>
@@ -354,44 +354,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>덴마크 그릭요거트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>리챔 오믈레햄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CJ제일제당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>롯데웰푸드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>풀무원 그릭요거트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고단백, 제로 슈거, 덴마크산 원료 등 프리미엄 속성을 갖춘 제품으로 출시</t>
-  </si>
-  <si>
-    <t>지난 10년간 시장 점유율 1위, 2023년 기준 39%의 점유율을 차지, 출시 10주년 누적 판매량 3억6000만개 돌파</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소잘라떼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>바리스타룰스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동원F&amp;B는 이 시장에서 약 0.7%의 미미한 점유율</t>
-  </si>
-  <si>
     <t>참치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -649,19 +615,203 @@
     <t>프리미엄 제품군의 헤비 유저 및 고급 식자재 채널 공략</t>
   </si>
   <si>
-    <t>매일 바이오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>쿠팡 기준 판매량 1위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>브랜드</t>
+  </si>
+  <si>
+    <t>제조사</t>
+  </si>
+  <si>
+    <t>주요 특징</t>
+  </si>
+  <si>
+    <t>100g당 가격대(원)</t>
+  </si>
+  <si>
+    <t>핵심 차별점</t>
+  </si>
+  <si>
+    <t>시장 점유율(%)</t>
+  </si>
+  <si>
+    <t>풀무원다논 그릭</t>
+  </si>
+  <si>
+    <t>풀무원다논</t>
+  </si>
+  <si>
+    <t>꾸덕한 질감, 높은 브랜드 인지도</t>
+  </si>
+  <si>
+    <t>~1,100</t>
+  </si>
+  <si>
+    <t>10년 연속 1위의 시장 지배력</t>
+  </si>
+  <si>
+    <t>덴마크 하이그릭</t>
+  </si>
+  <si>
+    <t>동원F&amp;B</t>
+  </si>
+  <si>
+    <t>고단백, 락토프리, 부드러운 질감</t>
+  </si>
+  <si>
+    <t>~995</t>
+  </si>
+  <si>
+    <t>국내 최초 주류 락토프리 그릭요거트</t>
+  </si>
+  <si>
+    <t>신제품</t>
+  </si>
+  <si>
+    <t>그릭데이</t>
+  </si>
+  <si>
+    <t>스위트바이오</t>
+  </si>
+  <si>
+    <t>수제 방식, 매우 꾸덕한 질감</t>
+  </si>
+  <si>
+    <t>~2,770</t>
+  </si>
+  <si>
+    <t>전문점 퀄리티의 프리미엄 포지션</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>매일바이오 플레인</t>
+  </si>
+  <si>
+    <t>매일유업</t>
+  </si>
+  <si>
+    <t>대중적인 플레인 요거트</t>
+  </si>
+  <si>
+    <t>~660</t>
+  </si>
+  <si>
+    <t>가격 경쟁력, 높은 접근성</t>
+  </si>
+  <si>
+    <t>커클랜드 시그니처</t>
+  </si>
+  <si>
+    <t>코스트코</t>
+  </si>
+  <si>
+    <t>대용량, 꾸덕한 질감, 가성비</t>
+  </si>
+  <si>
+    <t>~900</t>
+  </si>
+  <si>
+    <t>창고형 매장 기반의 가격 경쟁력</t>
+  </si>
+  <si>
+    <t>주력 형태</t>
+  </si>
+  <si>
+    <t>칸타타/레쓰비</t>
+  </si>
+  <si>
+    <t>롯데칠성</t>
+  </si>
+  <si>
+    <t>캔, NB캔</t>
+  </si>
+  <si>
+    <t>압도적인 시장 점유율, '국민 캔커피' 이미지</t>
+  </si>
+  <si>
+    <t>~35%</t>
+  </si>
+  <si>
+    <t>맥심 T.O.P</t>
+  </si>
+  <si>
+    <t>동서식품</t>
+  </si>
+  <si>
+    <t>캔, 컵</t>
+  </si>
+  <si>
+    <t>맥심' 브랜드의 높은 신뢰도, 프리미엄 원두</t>
+  </si>
+  <si>
+    <t>~13.4%</t>
+  </si>
+  <si>
+    <t>바리스타룰스</t>
+  </si>
+  <si>
+    <t>컵</t>
+  </si>
+  <si>
+    <t>컵커피 시장 1위, 상위 1% 원두 전문성 강조</t>
+  </si>
+  <si>
+    <t>소잘 라떼</t>
+  </si>
+  <si>
+    <t>락토프리' 기능성을 통한 소화 편의성 제공</t>
+  </si>
+  <si>
+    <t>돼지고기 함량(%)</t>
+  </si>
+  <si>
+    <t>나트륨(mg/100g)</t>
+  </si>
+  <si>
+    <t>CJ 스팸 클래식</t>
+  </si>
+  <si>
+    <t>CJ제일제당</t>
+  </si>
+  <si>
+    <t>오리지널리티, 짭짤하고 기름진 맛</t>
+  </si>
+  <si>
+    <t>~60%</t>
+  </si>
+  <si>
+    <t>동원 리챔 오리지널</t>
+  </si>
+  <si>
+    <t>짜지 않은 햄' 건강 지향 이미지</t>
+  </si>
+  <si>
+    <t>~20%</t>
+  </si>
+  <si>
+    <t>롯데 로스팜</t>
+  </si>
+  <si>
+    <t>롯데웰푸드</t>
+  </si>
+  <si>
+    <t>높은 단백질 함량</t>
+  </si>
+  <si>
+    <t>~6%</t>
+  </si>
+  <si>
+    <t>동원 리챔 오믈레햄</t>
+  </si>
+  <si>
+    <t>햄+계란+케첩'의 원캔(One-can) 편의성</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -682,6 +832,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -691,7 +849,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -729,11 +887,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -746,7 +919,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -755,6 +927,36 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2141,24 +2343,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9A48CC-CE39-4543-BD17-C89A51F5EDE2}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.296875" customWidth="1"/>
-    <col min="2" max="2" width="94" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" customWidth="1"/>
+    <col min="3" max="3" width="36.5" customWidth="1"/>
+    <col min="4" max="4" width="40.8984375" customWidth="1"/>
+    <col min="5" max="5" width="33.8984375" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -2166,7 +2372,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -2174,70 +2380,325 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="6" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
         <v>99</v>
       </c>
-      <c r="B9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="17" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>107</v>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" s="12">
+        <v>0.9244</v>
+      </c>
+      <c r="E24" s="13">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D25" s="12">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="E25" s="14">
+        <v>670</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" s="12">
+        <v>0.92159999999999997</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2258,76 +2719,76 @@
     <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="7" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>129</v>
+        <v>119</v>
+      </c>
+      <c r="B16" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2348,29 +2809,29 @@
     <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="4" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2390,457 +2851,457 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="8" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="D3" s="8">
+        <v>3991688</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="8">
+        <v>5502311</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="I2" s="7" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="8">
+        <v>2170055</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="I5" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="8" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="8">
+        <v>2977855</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D3" s="9">
-        <v>3991688</v>
-      </c>
-      <c r="E3" s="8" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="D7" s="8">
+        <v>1356230</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="9">
-        <v>5502311</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="H7" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="D8" s="8">
+        <v>339058</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" s="9">
-        <v>2170055</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="G8" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="D9" s="8">
+        <v>3445883</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="F9" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="8">
+        <v>861475</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" s="9">
-        <v>2977855</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="I10" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="D15" s="8">
+        <v>240602</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1356230</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="9">
-        <v>339058</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="9">
-        <v>3445883</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="9">
-        <v>861475</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="I15" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="8" t="s">
+    </row>
+    <row r="16" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="8">
+        <v>60150</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="8" t="s">
+      <c r="I16" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="9">
-        <v>240602</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="9">
-        <v>60150</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
